--- a/artfynd/A 62989-2025 artfynd.xlsx
+++ b/artfynd/A 62989-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130095915</v>
       </c>
       <c r="B2" t="n">
-        <v>81080</v>
+        <v>81165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62989-2025 artfynd.xlsx
+++ b/artfynd/A 62989-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130095915</v>
       </c>
       <c r="B2" t="n">
-        <v>81165</v>
+        <v>81168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62989-2025 artfynd.xlsx
+++ b/artfynd/A 62989-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130095915</v>
       </c>
       <c r="B2" t="n">
-        <v>81168</v>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
